--- a/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294705</t>
         </is>
       </c>
     </row>
@@ -897,6 +907,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293592</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294703</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294864</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102944304</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293596</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294863</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294885</t>
         </is>
       </c>
     </row>
@@ -1684,6 +1729,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102944379</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1799,6 +1849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294878</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1896,6 +1951,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102943389</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2011,6 +2071,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294214</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2108,6 +2173,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045387</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294212</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2326,6 +2401,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294701</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2437,6 +2517,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294704</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2549,6 +2634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294870</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2646,6 +2736,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045406</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2761,6 +2856,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294217</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2872,6 +2972,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294861</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2981,6 +3086,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294866</t>
         </is>
       </c>
     </row>
@@ -3098,6 +3208,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295272</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3209,6 +3324,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294860</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3320,6 +3440,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295266</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3417,6 +3542,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940353</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3514,6 +3644,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102994647</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3611,6 +3746,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045192</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3718,6 +3858,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294211</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3829,6 +3974,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294702</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3940,6 +4090,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294862</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4051,6 +4206,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294865</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4162,6 +4322,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294868</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4273,6 +4438,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294872</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4382,6 +4552,11 @@
       <c r="AY35" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295269</t>
         </is>
       </c>
     </row>
@@ -4499,6 +4674,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295271</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4608,6 +4788,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937920</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4717,6 +4902,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937936</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4814,6 +5004,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937937</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4936,6 +5131,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102944111</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5033,6 +5233,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937919</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5149,6 +5354,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294216</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5247,6 +5457,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937931</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5354,6 +5569,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294210</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5451,6 +5671,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940355</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5548,6 +5773,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940356</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5645,6 +5875,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940357</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5742,6 +5977,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102943373</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5839,6 +6079,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102943375</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5936,6 +6181,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045217</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6033,6 +6283,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045218</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6130,6 +6385,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045219</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6227,6 +6487,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045220</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6324,6 +6589,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045221</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6421,6 +6691,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045222</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6535,6 +6810,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293593</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6646,6 +6926,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294700</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6755,6 +7040,11 @@
       <c r="AY58" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294875</t>
         </is>
       </c>
     </row>
@@ -6872,6 +7162,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295273</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6987,6 +7282,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294219</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7098,6 +7398,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294859</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7209,6 +7514,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294873</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7320,6 +7630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295267</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7426,6 +7741,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294880</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7537,6 +7857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294884</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7634,6 +7959,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940358</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7731,6 +8061,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045287</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7828,6 +8163,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045405</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7925,6 +8265,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940354</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8022,6 +8367,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045194</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8136,6 +8486,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293595</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8256,6 +8611,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302458</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8363,6 +8723,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102944350</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8460,6 +8825,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937940</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8557,6 +8927,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102943376</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8671,6 +9046,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293594</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8782,6 +9162,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294683</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8893,6 +9278,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294679</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9004,6 +9394,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294695</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9115,6 +9510,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294689</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9226,6 +9626,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294687</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9333,6 +9738,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302459</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9444,6 +9854,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294692</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9551,6 +9966,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302461</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9658,6 +10078,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302462</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9765,6 +10190,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302460</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9885,6 +10315,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293589</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10004,6 +10439,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293591</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10115,6 +10555,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294682</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10212,6 +10657,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102943374</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10323,6 +10773,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294678</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10434,6 +10889,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294684</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10545,6 +11005,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294694</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10654,6 +11119,11 @@
       <c r="AY94" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294697</t>
         </is>
       </c>
     </row>
@@ -10770,6 +11240,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293590</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10881,8 +11356,110 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294685</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">

--- a/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">

--- a/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson</t>
+          <t>anders tedeholm, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
+          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson</t>
+          <t>anders tedeholm, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">

--- a/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294705</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135293592</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135294703</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135294864</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1253,7 +1253,7 @@
         <v>135293596</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>78826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>135294863</v>
       </c>
       <c r="B8" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1503,7 +1503,7 @@
         <v>135294885</v>
       </c>
       <c r="B9" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1740,7 +1740,7 @@
         <v>135294878</v>
       </c>
       <c r="B11" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1962,7 +1962,7 @@
         <v>135294214</v>
       </c>
       <c r="B13" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>135294212</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>135294701</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>135294704</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>135294870</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>135294217</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135294861</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2983,7 +2983,7 @@
         <v>135294866</v>
       </c>
       <c r="B22" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3099,7 +3099,7 @@
         <v>135295272</v>
       </c>
       <c r="B23" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>anders tedeholm, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3219,7 +3219,7 @@
         <v>135294860</v>
       </c>
       <c r="B24" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3335,7 +3335,7 @@
         <v>135295266</v>
       </c>
       <c r="B25" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3757,7 +3757,7 @@
         <v>135294211</v>
       </c>
       <c r="B29" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>135294702</v>
       </c>
       <c r="B30" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>135294862</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4101,7 +4101,7 @@
         <v>135294865</v>
       </c>
       <c r="B32" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4217,7 +4217,7 @@
         <v>135294868</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4333,7 +4333,7 @@
         <v>135294872</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4449,7 +4449,7 @@
         <v>135295269</v>
       </c>
       <c r="B35" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>135295271</v>
       </c>
       <c r="B36" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>135294216</v>
       </c>
       <c r="B42" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>135294210</v>
       </c>
       <c r="B44" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>135293593</v>
       </c>
       <c r="B56" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>135294700</v>
       </c>
       <c r="B57" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>135294875</v>
       </c>
       <c r="B58" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7053,7 +7053,7 @@
         <v>135295273</v>
       </c>
       <c r="B59" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>anders tedeholm, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7173,7 +7173,7 @@
         <v>135294219</v>
       </c>
       <c r="B60" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>135294859</v>
       </c>
       <c r="B61" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7409,7 +7409,7 @@
         <v>135294873</v>
       </c>
       <c r="B62" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7525,7 +7525,7 @@
         <v>135295267</v>
       </c>
       <c r="B63" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>135294880</v>
       </c>
       <c r="B64" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7752,7 +7752,7 @@
         <v>135294884</v>
       </c>
       <c r="B65" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -8378,7 +8378,7 @@
         <v>135293595</v>
       </c>
       <c r="B71" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>135302458</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>135293594</v>
       </c>
       <c r="B76" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>135294683</v>
       </c>
       <c r="B77" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>135294679</v>
       </c>
       <c r="B78" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>135294695</v>
       </c>
       <c r="B79" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>135294689</v>
       </c>
       <c r="B80" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>135294687</v>
       </c>
       <c r="B81" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135302459</v>
       </c>
       <c r="B82" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>135294692</v>
       </c>
       <c r="B83" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>135302461</v>
       </c>
       <c r="B84" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>135302462</v>
       </c>
       <c r="B85" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>135302460</v>
       </c>
       <c r="B86" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>135293589</v>
       </c>
       <c r="B87" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>135293591</v>
       </c>
       <c r="B88" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>135294682</v>
       </c>
       <c r="B89" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>135294678</v>
       </c>
       <c r="B91" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>135294684</v>
       </c>
       <c r="B92" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>135294694</v>
       </c>
       <c r="B93" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>135294697</v>
       </c>
       <c r="B94" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>135293590</v>
       </c>
       <c r="B95" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135294685</v>
       </c>
       <c r="B96" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294705</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135293592</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135294703</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135294864</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135293596</v>
       </c>
       <c r="B7" t="n">
-        <v>78826</v>
+        <v>78853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>135294863</v>
       </c>
       <c r="B8" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135294885</v>
       </c>
       <c r="B9" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135294878</v>
       </c>
       <c r="B11" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>135294214</v>
       </c>
       <c r="B13" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>135294212</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>135294701</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>135294704</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>135294870</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>135294217</v>
       </c>
       <c r="B20" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135294861</v>
       </c>
       <c r="B21" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>135294866</v>
       </c>
       <c r="B22" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>135295272</v>
       </c>
       <c r="B23" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>135294860</v>
       </c>
       <c r="B24" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>135295266</v>
       </c>
       <c r="B25" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>135294211</v>
       </c>
       <c r="B29" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>135294702</v>
       </c>
       <c r="B30" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>135294862</v>
       </c>
       <c r="B31" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>135294865</v>
       </c>
       <c r="B32" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>135294868</v>
       </c>
       <c r="B33" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>135294872</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>135295269</v>
       </c>
       <c r="B35" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>135295271</v>
       </c>
       <c r="B36" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>135294216</v>
       </c>
       <c r="B42" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>135294210</v>
       </c>
       <c r="B44" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>135293593</v>
       </c>
       <c r="B56" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>135294700</v>
       </c>
       <c r="B57" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>135294875</v>
       </c>
       <c r="B58" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>135295273</v>
       </c>
       <c r="B59" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>135294219</v>
       </c>
       <c r="B60" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>135294859</v>
       </c>
       <c r="B61" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>135294873</v>
       </c>
       <c r="B62" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>135295267</v>
       </c>
       <c r="B63" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>135294880</v>
       </c>
       <c r="B64" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>135294884</v>
       </c>
       <c r="B65" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>135293595</v>
       </c>
       <c r="B71" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>135293594</v>
       </c>
       <c r="B76" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>135294683</v>
       </c>
       <c r="B77" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>135294679</v>
       </c>
       <c r="B78" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>135294695</v>
       </c>
       <c r="B79" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>135294689</v>
       </c>
       <c r="B80" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>135294687</v>
       </c>
       <c r="B81" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135302459</v>
       </c>
       <c r="B82" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>135294692</v>
       </c>
       <c r="B83" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>135302461</v>
       </c>
       <c r="B84" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>135302462</v>
       </c>
       <c r="B85" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>135302460</v>
       </c>
       <c r="B86" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>135294678</v>
       </c>
       <c r="B91" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>135294684</v>
       </c>
       <c r="B92" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>135294694</v>
       </c>
       <c r="B93" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>135294697</v>
       </c>
       <c r="B94" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>135293590</v>
       </c>
       <c r="B95" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135294685</v>
       </c>
       <c r="B96" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
+++ b/artfynd/Västra Kikkejaure Rengärdet avvanm artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294705</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>135294214</v>
       </c>
       <c r="B13" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>135294216</v>
       </c>
       <c r="B42" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>135294210</v>
       </c>
       <c r="B44" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>135294689</v>
       </c>
       <c r="B80" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>135294687</v>
       </c>
       <c r="B81" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
